--- a/sheets/대금율보/검수/창원아리랑.xlsx
+++ b/sheets/대금율보/검수/창원아리랑.xlsx
@@ -2158,8 +2158,7 @@
         <is>
           <t xml:space="preserve">汰
 –ㄱ
-南
-‹</t>
+南</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -2169,8 +2168,7 @@
       </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">

--- a/sheets/대금율보/검수/창원아리랑.xlsx
+++ b/sheets/대금율보/검수/창원아리랑.xlsx
@@ -1871,16 +1871,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="81.63" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="91.25" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="91.25" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="91.25" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="91.25" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="E6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="91.25" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="25" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="91.25" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="91.25" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="91.25" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="E10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="91.25" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="91.25" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="91.25" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="91.25" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="91.25" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="91.25" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="91.25" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="91.25" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -2279,6 +2279,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
 </worksheet>
 </file>